--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Foundations Engineer</t>
+          <t>IT Support Specialist / Server Administrator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Dental Technology Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cherry Hill, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bc7b696fdd2052</t>
+          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
         </is>
       </c>
     </row>
@@ -678,52 +678,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93244101a55d1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,50 +766,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,15 +766,50 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IT Support Specialist / Server Administrator</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dental Technology Solutions</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cherry Hill, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>IT Support Specialist / Server Administrator</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Dental Technology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cherry Hill, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
+          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
+          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,77 +661,77 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d13983e0e25e706c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,15 +801,50 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cons - TC - AI and Data - Enterp Data - Data Eng and Arch - Data Eng - Mgr - MP - 1688246</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Google Cloud Platform, GCP, Hadoop, HDFS, Oracle</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493b62850523f4e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IT Support Specialist / Server Administrator</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dental Technology Solutions</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cherry Hill, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
+          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
         </is>
       </c>
     </row>
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
+          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,75 +776,250 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>EY</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D17" t="n">
         <v>10.4</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>AWS Cloud Architect- US Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RELQ TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior DevOps Engineer - Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>SportsBiz Group Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,139 +696,139 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,77 +951,322 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Java Trainer / Mentor / Educator</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>EY</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D22" t="n">
         <v>10.4</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Senior Big Data Engineer - AWS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d5b4bae86c5d93</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SportsBiz Group Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8be363a36eab12f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,42 +986,42 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
@@ -1098,52 +1098,52 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,24 +1186,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,15 +1256,50 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1121,59 +1121,59 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,124 +1182,299 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Identity AI / ML Engineer</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D30" t="n">
         <v>10.4</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Software Engineer III - Backend/Java</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect- US Remote</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RELQ TECHNOLOGIES</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>Software Engineer III - SDET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer - AWS</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, Hadoop, HDFS, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943257051095e0f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Java AWS Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metrixit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1156,29 +1156,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,54 +1301,54 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,108 +1357,108 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,122 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>AWS Cloud Architect- US Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>RELQ TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>IT Support Specialist / Server Administrator</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Dental Technology Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cherry Hill, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tex-Care Pharmacy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01469f91a410bc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Java AWS Developer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Metrixit</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,164 +811,164 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Java AWS Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Metrixit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,172 +1021,172 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Lodging by Liberty DBA Charter Furniture</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,147 +1441,392 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>EY</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>San Jose, CA, US USA</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D39" t="n">
         <v>10.4</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Identity AI / ML Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend/Java</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - SDET</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect- US Remote</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RELQ TECHNOLOGIES</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT Support Specialist / Server Administrator</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dental Technology Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cherry Hill, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tex-Care Pharmacy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01469f91a410bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Hadoop Developer-2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e23b4dd74e039ea</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java AWS Developer</t>
+          <t>Hadoop Developer-2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Metrixit</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
+          <t>https://www.indeed.com/viewjob?jk=2beea0b07c0483b5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,207 +986,207 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,49 +1231,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lodging by Liberty DBA Charter Furniture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134952c8e2b4c531</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,207 +1301,207 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,182 +1651,987 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Data Analyst, Customer Experience</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Jefferson, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Welltower, Inc</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Skywalk Global</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kafka Administrator</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Database Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Excelsior University</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kafka Cluster Support Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>10.4</v>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, ECS, IAM, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b2285059f147509</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Networking Trainee</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer(Azure + Python)-2</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ab4ff45664c5ad4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hadoop Developer-2</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e23b4dd74e039ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hadoop Developer-2</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, HDFS, Hive, Sqoop, MapReduce, Oozie, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2beea0b07c0483b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst, Customer Experience</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Jefferson, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
+          <t>https://www.indeed.com/viewjob?jk=b0883cd1c95d9570</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c6c7bd2fc0dd832</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=71b613f5fa6f42f2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Associate, Software Engineering: Java</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
+          <t>https://www.indeed.com/viewjob?jk=87f9ef2374336f8c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+          <t>https://www.indeed.com/viewjob?jk=233c238f31f0b2df</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=e3f1b7576de21e5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=061fd6d944b77a95</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=5568b0fcf2e4b1cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=6519f8163576c987</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,15 +2053,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=de0c61e17e14420b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec3c8b71c700b53</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=2907e4fc31b0b397</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,15 +2158,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=e8328caf9bb28e8d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Data Analyst, Customer Experience</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West Jefferson, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>IT Systems Engineer - Linux/Platform Operations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JMA Wireless</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,172 +2386,172 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer(Azure + Python)-2</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Databricks, Spark, Scala, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ab4ff45664c5ad4</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,42 +2596,672 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>SQL Database Administrator</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Database Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Excelsior University</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MLOps</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OnMed</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>White Plains, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b300a114f1bb0c85</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kafka Cluster Support Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Networking Trainee</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
           <t>Kafka</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>AK, US USA</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D80" t="n">
         <v>10.4</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0883cd1c95d9570</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c6c7bd2fc0dd832</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b613f5fa6f42f2</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87f9ef2374336f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=233c238f31f0b2df</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3f1b7576de21e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Analyst, Customer Experience</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Jefferson, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>IT Systems Engineer - Linux/Platform Operations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JMA Wireless</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061fd6d944b77a95</t>
+          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5568b0fcf2e4b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6519f8163576c987</t>
+          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de0c61e17e14420b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec3c8b71c700b53</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2907e4fc31b0b397</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8328caf9bb28e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst, Customer Experience</t>
+          <t>Security Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>West Jefferson, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Linux/Platform Operations</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>JMA Wireless</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate, Software Engineering: Java</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2687,11 +2687,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,108 +2757,108 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,332 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>OnMed</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>White Plains, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b300a114f1bb0c85</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Kafka Cluster Support Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Networking Trainee</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Software Engineer II - Data / ETL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Technical Architect (Node.js &amp; React.js)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>SLK America</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cf29a03b04d30c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
         </is>
       </c>
     </row>
@@ -1728,25 +1728,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Analyst, Customer Experience</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>West Jefferson, OH, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Linux/Platform Operations</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JMA Wireless</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate, Software Engineering: Java</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Analyst, Customer Experience</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>West Jefferson, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>IT Systems Engineer - Linux/Platform Operations</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>JMA Wireless</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2206,29 +2206,29 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Security Architect</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Security Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,24 +2726,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,24 +2761,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2936,17 +2936,332 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Networking Trainee</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior SDET - Performance Test Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CyberArk</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Software Engineer III - Backend/Java</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Software Engineer III - SDET</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AWS Cloud Architect- US Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RELQ TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - Data / ETL</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec636208e5ebd53d</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>IT Support Specialist / Server Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dental Technology Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cherry Hill, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>API Security IAM Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2fbf1e449d6461</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Architect (Node.js &amp; React.js)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SLK America</t>
+          <t>Tex-Care Pharmacy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sugar Land, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cf29a03b04d30c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d01469f91a410bc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,207 +1336,207 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=73661ff05dc86726</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Technical Architect (Node.js &amp; React.js)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>SLK America</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4cf29a03b04d30c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java AWS Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>Metrixit</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
+          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Energyby5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst, Customer Experience</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>West Jefferson, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Linux/Platform Operations</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JMA Wireless</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>Cloud Network Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=25bc7e36e114520d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate, Software Engineering: Java</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Application Developer Sr I</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IDEXX Laboratories</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, ME, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf035a827f29347</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Security Architect</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Analyst, Customer Experience</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Jefferson, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>DOCSIS Testing Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, NoSQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+          <t>https://www.indeed.com/viewjob?jk=277ddbd4a642c32d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
+          <t>IT Systems Engineer - Linux/Platform Operations</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>JMA Wireless</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,151 +2687,151 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+          <t>Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI Engineer , BI Center of Excellence</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Evolent</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kafka Cluster Support Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7e2aee8ab70eada4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Security Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tebra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Networking Trainee</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+          <t>S3, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+          <t>https://www.indeed.com/viewjob?jk=b70601a63d53974b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior SDET - Performance Test Engineer</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CyberArk</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Information Systems Architect - Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>DatamanUSA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4a2963fd5a1441</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kafka Production Support Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Analyst - Technical (Data Quality Analyst)-2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, Talend, Power BI, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,40 +3226,775 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+          <t>https://www.indeed.com/viewjob?jk=85e98320b32b1c20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EverCommerce - Sr. BI Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Evercommerce</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CT_NITRO Experimental AI Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>AMH</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BI Engineer , BI Center of Excellence</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Evolent</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Kafka Cluster Support Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Azure Network Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Networking Trainee</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior SDET - Performance Test Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CyberArk</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Kafka</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Kafka Production Support Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B102" t="inlineStr">
         <is>
           <t>Colgate-Palmolive</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D102" t="n">
         <v>10.4</v>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E102" t="inlineStr">
         <is>
           <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>

--- a/results/job_matches_2026-03-16.xlsx
+++ b/results/job_matches_2026-03-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cayuse Holdings</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a6b6e514fcadd1</t>
+          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend/Java</t>
+          <t>Senior Data Engineer &amp; Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1fd07d72b779f4</t>
+          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote)</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Flume, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b36bcd88655ec26b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer &amp; Architect</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fd769b82cca737f</t>
+          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6dc4080863d025</t>
+          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Azure Network Engineer</t>
+          <t>Kafka Schema Registry Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486e542e0314630</t>
+          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III - SDET</t>
+          <t>Data Engineer with Python</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95c7d23da1d85f79</t>
+          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -727,11 +727,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3d1545b725cacf9</t>
+          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, API Gateway, RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e62fa620ec25df7</t>
+          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer with Python</t>
+          <t>Kafka Data Streaming Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0b74cae84f6befa</t>
+          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, ECS, RDS, Azure, Databricks, Cloud Storage</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9727641069e970c0</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7128e441d147a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AWS Cloud Architect- US Remote</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RELQ TECHNOLOGIES</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a515f277b1dc9889</t>
+          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8674e111f05b66a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT Support Specialist / Server Administrator</t>
+          <t>Kafka Real Time Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dental Technology Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cherry Hill, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8efbf975313df8</t>
+          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kafka Data Streaming Consultant</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Five Guys</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24db9c74d80b856c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>(1383) Senior SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, Spark</t>
+          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5861e377dbf3fbc8</t>
+          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>IAM Helpdesk Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, API Gateway, IAM, Hadoop, Spark, Scala, Time Travel</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd06ecb9103a776</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>API Security IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, IAM, RDS, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2fbf1e449d6461</t>
+          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tex-Care Pharmacy</t>
+          <t>Sun Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sugar Land, TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d01469f91a410bc</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kafka Real Time Analytics Engineer</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Dataflow, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c52c30ca213c085f</t>
+          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Five Guys</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8d99a7003ab349</t>
+          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(1383) Senior SRE/DevOps Engineer</t>
+          <t>Software Engineer - TS/SCI with Polygraph</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Scala, SQL Server, DynamoDB, NoSQL, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8598ff2a82d03277</t>
+          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IAM Helpdesk Analyst</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, API Gateway, IAM, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,49 +1266,49 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5dd84afd435111</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Legion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Hive, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba6d16d92a70fded</t>
+          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Kafka Schema Registry Engineer</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73661ff05dc86726</t>
+          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00aacc39137daaf7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Network Operations Trainee</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sun Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,207 +1406,207 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1e43a65f53e347c</t>
+          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02bd3db44eac42a0</t>
+          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Spark, Scala, Kafka, SQL Server, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4083a7988b012418</t>
+          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a0681a75be4c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Technical Architect (Node.js &amp; React.js)</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SLK America</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4cf29a03b04d30c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Java AWS Developer</t>
+          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metrixit</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f7d16ccefe95913</t>
+          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - TS/SCI with Polygraph</t>
+          <t>Backend Developer - .NET &amp; Azure</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Dynamics Information Technology</t>
+          <t>Reidy</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, PostgreSQL, MySQL, ETL, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e85a55bb1da096e6</t>
+          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Legion</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bdd4694bf19ea44</t>
+          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1527cf38b699a4d</t>
+          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Kafka Streaming Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, IAM, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7aa69b55de4760</t>
+          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Network Operations Trainee</t>
+          <t>Kafka Data Replication Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88bda3516bc06812</t>
+          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Concord, NH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1811a5e61116c3b5</t>
+          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4f37aff04bbbf14</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Canton, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b6861263b7736a</t>
+          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Data Warehouse Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>New England Life Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Scarborough, ME, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a0e777ff5549418</t>
+          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Substantiation Platform Team *Hybrid*</t>
+          <t>Salesforce Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FundMate LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6027f8f887b28cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05145faabaee2e3b</t>
+          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5016f77a0e9f421</t>
+          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer Solution Design Focused</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Energyby5</t>
+          <t>UnyBrands</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, Step Functions, ECS, IAM, RDS, MySQL, DynamoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a5059671136ac6d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4181653d522a2852</t>
+          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Kafka Streaming Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Knightscope, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,14 +2106,14 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4379abeabd8c87ca</t>
+          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kafka Data Replication Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c99b3c52b9b8bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Network Architect</t>
+          <t>Kafka Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2162,11 +2162,11 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, Databricks, Spark, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25bc7e36e114520d</t>
+          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Developer - .NET &amp; Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Reidy</t>
+          <t>Kimco Realty Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96c56aac4e4e49c2</t>
+          <t>https://www.indeed.com/viewjob?jk=1af2172268615fcb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Application Developer Sr II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Concord, NH, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=239b1046f06d3d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=c032bd6bc3e68c33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>Application Developer Sr I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>IDEXX Laboratories</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, Databricks, Snowflake, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7f6dab575a97ad</t>
+          <t>https://www.indeed.com/viewjob?jk=89582c128a65ea29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Canton, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d02a598ce56d257c</t>
+          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Warehouse Developer</t>
+          <t>SQL DBA/ Data Engineer- AWS Migration</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New England Life Care</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scarborough, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b64bf3747c350d3</t>
+          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Salesforce Developer</t>
+          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FundMate LLC</t>
+          <t>Welltower, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d833bbf779bc5e9f</t>
+          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Skywalk Global</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8817cb3ef7265196</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>SQL Database Administrator</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e563fec6aa7f64cb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Data Engineer Solution Design Focused</t>
+          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>UnyBrands</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d83c96f81842df2</t>
+          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer – Ontology &amp; Semantic Modeling</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d5fa75dac6e177</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, ECS, RDS, Azure, Scala, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=929003fb57aecac9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Analyst, Customer Experience</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RH</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>West Jefferson, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, MySQL, NoSQL, ETL, Power BI</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67099b1137583cca</t>
+          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DOCSIS Testing Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, NoSQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=277ddbd4a642c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, PostgreSQL, MySQL, MongoDB, NoSQL, Jenkins, Maven, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f452a32fedc556a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT Systems Engineer - Linux/Platform Operations</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JMA Wireless</t>
+          <t>Excelsior University</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c45683c60eeacd5</t>
+          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kafka Administrator</t>
+          <t>AI Industry 5.0 Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bloom Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, MySQL, MongoDB, Tableau, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b37f08f8afa136e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd1a549fc1388c4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,102 +2771,102 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=016f2662bb776d79</t>
+          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate, Software Engineering: Java</t>
+          <t>EverCommerce - Sr. BI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Kafka, PostgreSQL, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84fa61fcf21b8414</t>
+          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SQL DBA/ Data Engineer- AWS Migration</t>
+          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211072bc9ba0394d</t>
+          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer - onsite Dallas, TX</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Welltower, Inc</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=966b58a59ad0b785</t>
+          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>BI Engineer , BI Center of Excellence</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Skywalk Global</t>
+          <t>Evolent</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c074eb3bed74ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SQL Database Administrator</t>
+          <t>Kafka Cluster Support Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, RDS, Snowflake, SQL Server, PostgreSQL, DynamoDB</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a3b76cb2a8af4e3</t>
+          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Azure Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Jenkins, Maven, Docker</t>
+          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e2aee8ab70eada4</t>
+          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Security Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tebra</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3f0014b8bc7264</t>
+          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Scala, Kafka, Oracle, CI/CD, Jenkins, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b70601a63d53974b</t>
+          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java/SpringBoot/Kafka/Cloud)</t>
+          <t>Networking Trainee</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, Cassandra, NoSQL, Splunk</t>
+          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a1692fa5839e7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Information Systems Architect - Consultant</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DatamanUSA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, Azure, Scala, CI/CD, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4a2963fd5a1441</t>
+          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Kafka Production Support Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, HBase, Spark, Kafka, MLOps, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4ec3a15ea80839</t>
+          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Excelsior University</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, ETL, Pentaho, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85fa6c830bb1cd62</t>
+          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analyst - Technical (Data Quality Analyst)-2</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, Talend, Power BI, Tableau, Splunk</t>
+          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85e98320b32b1c20</t>
+          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Commercial Operations BI Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3260,741 +3260,6 @@
         </is>
       </c>
       <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5ccd49d302b2f7b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=508cf5fa2697a154</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=641aca644ab6b5a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78876821e7b218f</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, ETL, Power BI, Tableau, MLOps, CI/CD</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c56aa2c78fe94ad7</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>EverCommerce - Sr. BI Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Evercommerce</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, Star Schema, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96fcb774adfa1d8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>AI &amp; Machine Learning Engineering Consultant - Life Sciences Sector - Senior - Consulting</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Spark, Scala, MLOps, CI/CD, Azure DevOps, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=230bad3331a7b81d</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Docker, AKS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fecf1fa5246a7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Scientist-Tech Con-AI and Data-AI and Quan Modelling-Azure Data Scientist-Mgr-Mult Pos-1680332</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>EY</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, MLflow, Kubernetes, AKS, Python</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-28</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b613410a2f36e193</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>AMH</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Draper, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Splunk, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6de9642d876b3baf</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>BI Engineer , BI Center of Excellence</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Evolent</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, SQL Server, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9ecdd9a09c5fe384</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Kafka Cluster Support Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35509e20006036e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Azure Network Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Azure, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Fact Tables, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=276783735764b1c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Snowflake, NoSQL, Splunk, Jenkins, Terraform</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f18a97d1887b5ea</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, DynamoDB, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=80d0b043bab9a938</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Networking Trainee</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, Kafka, SQL Server, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd68d8034b98c3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior SDET - Performance Test Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>CyberArk</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=64e75a054f0e88a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Terraform, Kubernetes, SonarQube</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f090126c2e636f7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Engineer â€“ SIEM Platform Engineering &amp; Operations</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Bank of America</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Splunk, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd8574275eb972b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Kafka</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, RDS, Databricks, Event Hubs, Spark, PySpark, Scala, Kafka, ELT</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57504132804a2fda</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Kafka Production Support Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94e5c794f9af11e6</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a8f866ceafbf4452</t>
         </is>
